--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OHIO_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OHIO_2021.xlsx
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="4">
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="D9">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="10">
@@ -571,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="13">
@@ -625,7 +625,7 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="16">
@@ -1093,7 +1093,7 @@
         <v>4</v>
       </c>
       <c r="D41">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="42">
@@ -1903,7 +1903,7 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="87">
@@ -2155,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="D100">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="101">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="D109">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="110">
@@ -2353,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="D111">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="112">
@@ -2551,7 +2551,7 @@
         <v>4</v>
       </c>
       <c r="D122">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="123">
@@ -2695,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="D130">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="131">
@@ -3019,7 +3019,7 @@
         <v>4</v>
       </c>
       <c r="D148">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="149">
@@ -3307,7 +3307,7 @@
         <v>4</v>
       </c>
       <c r="D164">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="165">
@@ -3541,7 +3541,7 @@
         <v>4</v>
       </c>
       <c r="D177">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="178">
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
       <c r="D185">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="186">
@@ -3703,7 +3703,7 @@
         <v>4</v>
       </c>
       <c r="D186">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="187">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C195">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C204">
@@ -4261,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="D217">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="218">
@@ -4891,7 +4891,7 @@
         <v>4</v>
       </c>
       <c r="D252">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="253">
@@ -5035,7 +5035,7 @@
         <v>4</v>
       </c>
       <c r="D260">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="261">
@@ -5179,7 +5179,7 @@
         <v>4</v>
       </c>
       <c r="D268">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="269">
@@ -5269,7 +5269,7 @@
         <v>4</v>
       </c>
       <c r="D273">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="274">
@@ -5467,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="D284">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="285">
@@ -5647,7 +5647,7 @@
         <v>4</v>
       </c>
       <c r="D294">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="295">
@@ -5953,7 +5953,7 @@
         <v>4</v>
       </c>
       <c r="D311">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="312">
@@ -5989,7 +5989,7 @@
         <v>4</v>
       </c>
       <c r="D313">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="314">
@@ -6313,7 +6313,7 @@
         <v>4</v>
       </c>
       <c r="D331">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="332">
@@ -6979,7 +6979,7 @@
         <v>4</v>
       </c>
       <c r="D368">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="369">
@@ -7213,7 +7213,7 @@
         <v>41</v>
       </c>
       <c r="D381">
-        <v>0.009259259259259259</v>
+        <v>0.00925925925925926</v>
       </c>
     </row>
     <row r="382">
@@ -7537,7 +7537,7 @@
         <v>42</v>
       </c>
       <c r="D399">
-        <v>0.009485094850948509</v>
+        <v>0.009485094850948507</v>
       </c>
     </row>
     <row r="400">
@@ -7933,7 +7933,7 @@
         <v>4</v>
       </c>
       <c r="D421">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="422">
@@ -7987,7 +7987,7 @@
         <v>4</v>
       </c>
       <c r="D424">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="425">
@@ -8275,7 +8275,7 @@
         <v>4</v>
       </c>
       <c r="D440">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="441">
@@ -8617,7 +8617,7 @@
         <v>4</v>
       </c>
       <c r="D459">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="460">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C515">
         <v>4</v>
       </c>
       <c r="D515">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="516">
@@ -10104,14 +10104,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C542">
         <v>4</v>
       </c>
       <c r="D542">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="543">
@@ -10237,7 +10237,7 @@
         <v>4</v>
       </c>
       <c r="D549">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="550">
@@ -10417,7 +10417,7 @@
         <v>4</v>
       </c>
       <c r="D559">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="560">
@@ -10597,7 +10597,7 @@
         <v>4</v>
       </c>
       <c r="D569">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="570">
@@ -10849,7 +10849,7 @@
         <v>4</v>
       </c>
       <c r="D583">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="584">
@@ -10975,7 +10975,7 @@
         <v>4</v>
       </c>
       <c r="D590">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="591">
@@ -11065,7 +11065,7 @@
         <v>4</v>
       </c>
       <c r="D595">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="596">
@@ -11263,7 +11263,7 @@
         <v>4</v>
       </c>
       <c r="D606">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="607">
@@ -11911,7 +11911,7 @@
         <v>4</v>
       </c>
       <c r="D642">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="643">
@@ -11929,7 +11929,7 @@
         <v>4</v>
       </c>
       <c r="D643">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="644">
@@ -12127,7 +12127,7 @@
         <v>4</v>
       </c>
       <c r="D654">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="655">
@@ -12145,7 +12145,7 @@
         <v>4</v>
       </c>
       <c r="D655">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="656">
@@ -12361,7 +12361,7 @@
         <v>4</v>
       </c>
       <c r="D667">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="668">
@@ -12397,7 +12397,7 @@
         <v>4</v>
       </c>
       <c r="D669">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="670">
@@ -12649,7 +12649,7 @@
         <v>4</v>
       </c>
       <c r="D683">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="684">
@@ -13279,7 +13279,7 @@
         <v>4</v>
       </c>
       <c r="D718">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="719">
@@ -13333,7 +13333,7 @@
         <v>4</v>
       </c>
       <c r="D721">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="722">
@@ -13495,7 +13495,7 @@
         <v>4</v>
       </c>
       <c r="D730">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="731">
@@ -13675,7 +13675,7 @@
         <v>4</v>
       </c>
       <c r="D740">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="741">
@@ -14413,7 +14413,7 @@
         <v>4</v>
       </c>
       <c r="D781">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="782">
@@ -14575,7 +14575,7 @@
         <v>4</v>
       </c>
       <c r="D790">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="791">
@@ -14755,7 +14755,7 @@
         <v>4</v>
       </c>
       <c r="D800">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="801">
@@ -14971,7 +14971,7 @@
         <v>4</v>
       </c>
       <c r="D812">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="813">
@@ -15169,7 +15169,7 @@
         <v>4</v>
       </c>
       <c r="D823">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="824">
@@ -15259,7 +15259,7 @@
         <v>4</v>
       </c>
       <c r="D828">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="829">
@@ -15277,7 +15277,7 @@
         <v>4</v>
       </c>
       <c r="D829">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="830">
@@ -15457,7 +15457,7 @@
         <v>4</v>
       </c>
       <c r="D839">
-        <v>0.0009033423667570009</v>
+        <v>0.0009033423667570008</v>
       </c>
     </row>
     <row r="840">
